--- a/rules/NEW-RULE/positive/02/data/new-rule-positive-02.xlsx
+++ b/rules/NEW-RULE/positive/02/data/new-rule-positive-02.xlsx
@@ -35,7 +35,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -57,9 +61,10 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <i/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -67,6 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -96,13 +107,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,18 +449,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -464,18 +476,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>ts.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Trial Summary Parameters</v>
       </c>
     </row>
@@ -491,174 +503,174 @@
   <dimension ref="A1:K5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>TSSEQ</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>TSGRPID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>TSPARMCD</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>TSPARM</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>TSVAL</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>TSVALNF</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>TSVALCD</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>TSVCDREF</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>TSVCDVER</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="6" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="4" t="str">
+      <c r="E2" s="6" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="4" t="str">
+      <c r="F2" s="6" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="4" t="str">
+      <c r="G2" s="6" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="4" t="str">
+      <c r="H2" s="6" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="4" t="str">
+      <c r="I2" s="6" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="4" t="str">
+      <c r="J2" s="6" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="4" t="str">
+      <c r="K2" s="6" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="4" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="4" t="str">
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="6" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>8</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="6">
         <v>200</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="6">
         <v>8</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="6">
         <v>40</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="6">
         <v>200</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="6">
         <v>4</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="6">
         <v>200</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="6">
         <v>200</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="6">
         <v>200</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="3" t="str">
         <v>TS</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="str">
+      <c r="D5" s="3" t="str">
         <v/>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="E5" s="3" t="str">
         <v>SSTDTC</v>
       </c>
-      <c r="F5" s="5" t="str">
+      <c r="F5" s="3" t="str">
         <v>Study Start Date</v>
       </c>
-      <c r="G5" s="5" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="H5" s="2" t="str">
+      <c r="G5" s="3" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="H5" s="3" t="str">
         <v/>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="I5" s="3" t="str">
         <v/>
       </c>
-      <c r="J5" s="5" t="str">
+      <c r="J5" s="3" t="str">
         <v>ISO 8601</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/02/data/new-rule-positive-02.xlsx
+++ b/rules/NEW-RULE/positive/02/data/new-rule-positive-02.xlsx
@@ -5,7 +5,8 @@
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="ae.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="ts.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -61,10 +62,10 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -72,12 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -114,7 +109,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,7 +468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -484,22 +479,441 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="2" t="str">
+        <v>ae.xpt</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Adverse Events</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="str">
         <v>ts.xpt</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B3" s="3" t="str">
         <v>Trial Summary Parameters</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>AESEQ</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>AETERM</v>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v>AESEV</v>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v>AESER</v>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v>AEACN</v>
+      </c>
+      <c r="I1" s="4" t="str">
+        <v>AEREL</v>
+      </c>
+      <c r="J1" s="4" t="str">
+        <v>AEOUT</v>
+      </c>
+      <c r="K1" s="4" t="str">
+        <v>AESCAN</v>
+      </c>
+      <c r="L1" s="4" t="str">
+        <v>AESCONG</v>
+      </c>
+      <c r="M1" s="4" t="str">
+        <v>AESDISAB</v>
+      </c>
+      <c r="N1" s="4" t="str">
+        <v>AESDTH</v>
+      </c>
+      <c r="O1" s="4" t="str">
+        <v>AESHOSP</v>
+      </c>
+      <c r="P1" s="4" t="str">
+        <v>AESLIFE</v>
+      </c>
+      <c r="Q1" s="4" t="str">
+        <v>AESOD</v>
+      </c>
+      <c r="R1" s="4" t="str">
+        <v>AESMIE</v>
+      </c>
+      <c r="S1" s="4" t="str">
+        <v>AECONTRT</v>
+      </c>
+      <c r="T1" s="4" t="str">
+        <v>EPOCH</v>
+      </c>
+      <c r="U1" s="4" t="str">
+        <v>AESTDTC</v>
+      </c>
+      <c r="V1" s="4" t="str">
+        <v>AEENDTC</v>
+      </c>
+      <c r="W1" s="4" t="str">
+        <v>AESTDY</v>
+      </c>
+      <c r="X1" s="4" t="str">
+        <v>AEENDY</v>
+      </c>
+      <c r="Y1" s="4" t="str">
+        <v>AEENRTPT</v>
+      </c>
+      <c r="Z1" s="4" t="str">
+        <v>AEENTPT</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v>Sequence Number</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v>Reported Term for the Adverse Event</v>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v>Severity/Intensity</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>Serious Event</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>Action Taken with Study Treatment</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <v>Causality</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <v>Outcome of Adverse Event</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <v>Involves Cancer</v>
+      </c>
+      <c r="L2" s="5" t="str">
+        <v>Congenital Anomaly or Birth Defect</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <v>Persist or Signif Disability/Incapacity</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <v>Results in Death</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <v>Requires or Prolongs Hospitalization</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>Is Life Threatening</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <v>Occurred with Overdose</v>
+      </c>
+      <c r="R2" s="5" t="str">
+        <v>Other Medically Important Serious Event</v>
+      </c>
+      <c r="S2" s="5" t="str">
+        <v>Concomitant or Additional Trtmnt Given</v>
+      </c>
+      <c r="T2" s="5" t="str">
+        <v>Epoch</v>
+      </c>
+      <c r="U2" s="5" t="str">
+        <v>Start Date/Time of Adverse Event</v>
+      </c>
+      <c r="V2" s="5" t="str">
+        <v>End Date/Time of Adverse Event</v>
+      </c>
+      <c r="W2" s="5" t="str">
+        <v>Study Day of Start of Adverse Event</v>
+      </c>
+      <c r="X2" s="5" t="str">
+        <v>Study Day of End of Adverse Event</v>
+      </c>
+      <c r="Y2" s="5" t="str">
+        <v>End Relative to Reference Time Point</v>
+      </c>
+      <c r="Z2" s="5" t="str">
+        <v>End Reference Time Point</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="X3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="Y3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="5" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5">
+        <v>50</v>
+      </c>
+      <c r="N4" s="5">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5">
+        <v>50</v>
+      </c>
+      <c r="P4" s="5">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>50</v>
+      </c>
+      <c r="R4" s="5">
+        <v>50</v>
+      </c>
+      <c r="S4" s="5">
+        <v>50</v>
+      </c>
+      <c r="T4" s="5">
+        <v>50</v>
+      </c>
+      <c r="U4" s="5">
+        <v>50</v>
+      </c>
+      <c r="V4" s="5">
+        <v>50</v>
+      </c>
+      <c r="W4" s="5">
+        <v>8</v>
+      </c>
+      <c r="X4" s="5">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <v>INJECTION SITE REACTION</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <v>MODERATE</v>
+      </c>
+      <c r="G5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="H5" s="6" t="str">
+        <v>DRUG WITHDRAWN</v>
+      </c>
+      <c r="I5" s="6" t="str">
+        <v>RELATED</v>
+      </c>
+      <c r="J5" s="6" t="str">
+        <v>NOT RECOVERED/NOT RESOLVED</v>
+      </c>
+      <c r="K5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="L5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="M5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="N5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="O5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="P5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="Q5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="R5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="S5" s="6" t="str">
+        <v>N</v>
+      </c>
+      <c r="T5" s="6" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="U5" s="6">
+        <v>41245</v>
+      </c>
+      <c r="V5" s="6" t="str">
+        <v/>
+      </c>
+      <c r="W5" s="6">
+        <v>3</v>
+      </c>
+      <c r="X5" s="6" t="str">
+        <v/>
+      </c>
+      <c r="Y5" s="6" t="str">
+        <v>ONGOING</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>41414</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetData>
     <row r="1">
@@ -541,104 +955,104 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>200</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>200</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>4</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>200</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>200</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>200</v>
       </c>
     </row>
